--- a/branches/ee/StructureDefinition-IdentifiableMedication.xlsx
+++ b/branches/ee/StructureDefinition-IdentifiableMedication.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-26T18:31:17+00:00</t>
+    <t>2022-08-26T18:32:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ee/StructureDefinition-IdentifiableMedication.xlsx
+++ b/branches/ee/StructureDefinition-IdentifiableMedication.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-26T18:32:22+00:00</t>
+    <t>2022-08-26T18:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ee/StructureDefinition-IdentifiableMedication.xlsx
+++ b/branches/ee/StructureDefinition-IdentifiableMedication.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-26T18:49:33+00:00</t>
+    <t>2022-08-26T18:49:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ee/StructureDefinition-IdentifiableMedication.xlsx
+++ b/branches/ee/StructureDefinition-IdentifiableMedication.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-26T18:49:52+00:00</t>
+    <t>2022-08-26T18:58:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ee/StructureDefinition-IdentifiableMedication.xlsx
+++ b/branches/ee/StructureDefinition-IdentifiableMedication.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-26T18:58:18+00:00</t>
+    <t>2022-08-26T19:11:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
